--- a/TermProject/exponentiationfsm_state_table.xlsx
+++ b/TermProject/exponentiationfsm_state_table.xlsx
@@ -5,11 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="rsa_core_fsm" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Ark1" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="exponentsiation_fsm" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="45">
   <si>
     <t xml:space="preserve">Inputs</t>
   </si>
@@ -104,28 +104,58 @@
     <t xml:space="preserve">FINISHED</t>
   </si>
   <si>
+    <t xml:space="preserve">inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action on signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ready_out </t>
+  </si>
+  <si>
+    <t xml:space="preserve">load_result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valid_out </t>
+  </si>
+  <si>
     <t xml:space="preserve">current state</t>
   </si>
   <si>
     <t xml:space="preserve">next state</t>
   </si>
   <si>
-    <t xml:space="preserve">ready_out </t>
-  </si>
-  <si>
-    <t xml:space="preserve">load_result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valid_out </t>
-  </si>
-  <si>
     <t xml:space="preserve">reset</t>
   </si>
   <si>
     <t xml:space="preserve">counting</t>
   </si>
   <si>
+    <t xml:space="preserve">Counter = counter + 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">finished</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter =  counter + 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if valid_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r_reg &lt;= </t>
   </si>
 </sst>
 </file>
@@ -201,7 +231,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -216,6 +246,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -948,172 +982,310 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G10"/>
+  <dimension ref="B2:K28"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="10.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.89"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12.05"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="21.08"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="10.6"/>
+  </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E2" s="0" t="s">
+      <c r="B2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>31</v>
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
+      <c r="B7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>1</v>
+      <c r="B9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>1</v>
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/TermProject/exponentiationfsm_state_table.xlsx
+++ b/TermProject/exponentiationfsm_state_table.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="66">
   <si>
     <t xml:space="preserve">Inputs</t>
   </si>
@@ -53,6 +53,12 @@
     <t xml:space="preserve">counter</t>
   </si>
   <si>
+    <t xml:space="preserve">Current_state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next_state</t>
+  </si>
+  <si>
     <t xml:space="preserve">msgin_ready</t>
   </si>
   <si>
@@ -68,21 +74,15 @@
     <t xml:space="preserve">new_msg_neg</t>
   </si>
   <si>
-    <t xml:space="preserve">Current_state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next_state</t>
-  </si>
-  <si>
     <t xml:space="preserve">dc</t>
   </si>
   <si>
+    <t xml:space="preserve">LOAD_NEW_MSG</t>
+  </si>
+  <si>
     <t xml:space="preserve">x</t>
   </si>
   <si>
-    <t xml:space="preserve">LOAD_NEW_MSG</t>
-  </si>
-  <si>
     <t xml:space="preserve">COUNT_WAIT</t>
   </si>
   <si>
@@ -122,12 +122,21 @@
     <t xml:space="preserve">ready_out </t>
   </si>
   <si>
+    <t xml:space="preserve">mux_control_in[7..0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a[255..0]</t>
+  </si>
+  <si>
     <t xml:space="preserve">load_result</t>
   </si>
   <si>
     <t xml:space="preserve">Counter</t>
   </si>
   <si>
+    <t xml:space="preserve">mux_control_out[8..0]</t>
+  </si>
+  <si>
     <t xml:space="preserve">valid_out </t>
   </si>
   <si>
@@ -152,10 +161,64 @@
     <t xml:space="preserve">Counter =  counter + 1</t>
   </si>
   <si>
-    <t xml:space="preserve">if valid_out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r_reg &lt;= </t>
+    <t xml:space="preserve">mux_ctrl_R_in[3..0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R_OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A[255]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5[256]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4[256]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3[256]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2[256]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5 = !A[255] &amp;&amp; !mux_ctrl_R_in[3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mux_ctrl_P_in[3..0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S11[256]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10[256]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9[256]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8[256]</t>
   </si>
 </sst>
 </file>
@@ -165,7 +228,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +250,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -231,25 +302,49 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -441,36 +536,36 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD21"/>
+  <dimension ref="A1:XFD30"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="26.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="2" width="19.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="14.2"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="13.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="N1" s="0" t="s">
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -514,7 +609,7 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="XFD2" s="0"/>
+      <c r="XFD2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -536,27 +631,27 @@
         <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="3"/>
+      <c r="N3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -577,14 +672,14 @@
       <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>0</v>
@@ -592,13 +687,13 @@
       <c r="K4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" s="3"/>
+      <c r="L4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -619,14 +714,14 @@
       <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0</v>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>0</v>
@@ -634,13 +729,13 @@
       <c r="K5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="0" t="s">
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -663,28 +758,28 @@
       <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0</v>
+      <c r="G6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="3"/>
+      <c r="L6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -705,28 +800,28 @@
       <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0</v>
+      <c r="G7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="3"/>
+      <c r="L7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -747,28 +842,28 @@
       <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0</v>
+      <c r="G8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -789,28 +884,28 @@
       <c r="F9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0</v>
+      <c r="G9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -833,28 +928,28 @@
       <c r="F10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>0</v>
+      <c r="G10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -875,26 +970,26 @@
       <c r="F11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
+      <c r="G11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -916,56 +1011,110 @@
       <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>1</v>
+      <c r="G12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="0"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="0"/>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="0"/>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="0"/>
+      <c r="F17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="0"/>
+      <c r="F18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="0"/>
+      <c r="F19" s="2"/>
+      <c r="K19" s="0"/>
+      <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="0"/>
+      <c r="F20" s="2"/>
+      <c r="K20" s="0"/>
+      <c r="L20" s="0"/>
+      <c r="M20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="0"/>
+      <c r="F21" s="2"/>
+      <c r="K21" s="0"/>
+      <c r="L21" s="0"/>
+      <c r="M21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K22" s="0"/>
+      <c r="L22" s="0"/>
+      <c r="M22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K23" s="0"/>
+      <c r="L23" s="0"/>
+      <c r="M23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K24" s="0"/>
+      <c r="L24" s="0"/>
+      <c r="M24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K25" s="0"/>
+      <c r="L25" s="0"/>
+      <c r="M25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" s="0"/>
+      <c r="L26" s="0"/>
+      <c r="M26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" s="0"/>
+      <c r="L27" s="0"/>
+      <c r="M27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K28" s="0"/>
+      <c r="L28" s="0"/>
+      <c r="M28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" s="0"/>
+      <c r="L29" s="0"/>
+      <c r="M29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" s="0"/>
+      <c r="L30" s="0"/>
+      <c r="M30" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="I1:M1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -982,38 +1131,47 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:K28"/>
-  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:N113"/>
+  <sheetFormatPr defaultColWidth="10.60546875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="10.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.89"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12.05"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.13"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="21.08"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="10.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20.38"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="1" width="10.61"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="5"/>
+      <c r="N2" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1025,25 +1183,34 @@
         <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>37</v>
+      <c r="L3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1056,25 +1223,27 @@
       <c r="D4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1088,25 +1257,27 @@
       <c r="D5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1117,26 +1288,28 @@
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>40</v>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1146,26 +1319,28 @@
       <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>40</v>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1175,26 +1350,28 @@
       <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>42</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1204,23 +1381,25 @@
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1" t="s">
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1233,11 +1412,13 @@
       <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>41</v>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="L10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1250,41 +1431,1432 @@
       <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>38</v>
-      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0"/>
+      <c r="B24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A27" s="0"/>
+      <c r="B27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E28" s="1" t="s">
-        <v>44</v>
+      <c r="A28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="0"/>
+      <c r="D28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="0"/>
+      <c r="F29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D33" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D34" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0"/>
+      <c r="D35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D36" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D37" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D39" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D40" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D41" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0"/>
+      <c r="B42" s="10"/>
+      <c r="D42" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0"/>
+      <c r="D43" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7"/>
+      <c r="D44" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D45" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D46" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D47" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D48" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D49" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D50" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D51" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D52" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D53" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D54" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D55" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D56" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D57" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D58" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D59" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D60" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D61" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D62" s="0"/>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0"/>
+      <c r="G62" s="0"/>
+      <c r="H62" s="0"/>
+      <c r="I62" s="0"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D63" s="0"/>
+      <c r="E63" s="0"/>
+      <c r="F63" s="0"/>
+      <c r="G63" s="0"/>
+      <c r="H63" s="0"/>
+      <c r="I63" s="0"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D64" s="0"/>
+      <c r="E64" s="0"/>
+      <c r="F64" s="0"/>
+      <c r="G64" s="0"/>
+      <c r="H64" s="0"/>
+      <c r="I64" s="0"/>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D65" s="0"/>
+      <c r="E65" s="0"/>
+      <c r="F65" s="0"/>
+      <c r="G65" s="0"/>
+      <c r="H65" s="0"/>
+      <c r="I65" s="0"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D66" s="0"/>
+      <c r="E66" s="0"/>
+      <c r="F66" s="0"/>
+      <c r="G66" s="0"/>
+      <c r="H66" s="0"/>
+      <c r="I66" s="0"/>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D67" s="0"/>
+      <c r="E67" s="0"/>
+      <c r="F67" s="0"/>
+      <c r="G67" s="0"/>
+      <c r="H67" s="0"/>
+      <c r="I67" s="0"/>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D68" s="0"/>
+      <c r="E68" s="0"/>
+      <c r="F68" s="0"/>
+      <c r="G68" s="0"/>
+      <c r="H68" s="0"/>
+      <c r="I68" s="0"/>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D69" s="0"/>
+      <c r="E69" s="0"/>
+      <c r="F69" s="0"/>
+      <c r="G69" s="0"/>
+      <c r="H69" s="0"/>
+      <c r="I69" s="0"/>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D70" s="0"/>
+      <c r="E70" s="0"/>
+      <c r="F70" s="0"/>
+      <c r="G70" s="0"/>
+      <c r="H70" s="0"/>
+      <c r="I70" s="0"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E81" s="0"/>
+      <c r="F81" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E88" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:F2"/>
+  <mergeCells count="6">
+    <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="F80:I80"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/TermProject/exponentiationfsm_state_table.xlsx
+++ b/TermProject/exponentiationfsm_state_table.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="72">
   <si>
     <t xml:space="preserve">Inputs</t>
   </si>
@@ -215,10 +215,28 @@
     <t xml:space="preserve">S10[256]</t>
   </si>
   <si>
+    <t xml:space="preserve">S11</t>
+  </si>
+  <si>
     <t xml:space="preserve">S9[256]</t>
   </si>
   <si>
     <t xml:space="preserve">S8[256]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6</t>
   </si>
 </sst>
 </file>
@@ -1142,8 +1160,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.13"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="21.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20.38"/>
@@ -2294,6 +2312,9 @@
       <c r="B82" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="D82" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="E82" s="7" t="n">
         <v>0</v>
       </c>
@@ -2315,6 +2336,9 @@
         <v>1</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D83" s="8" t="s">
         <v>64</v>
       </c>
       <c r="E83" s="7" t="n">
@@ -2338,7 +2362,10 @@
         <v>0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="E84" s="7" t="n">
         <v>0</v>
@@ -2357,6 +2384,9 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D85" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
       </c>
@@ -2374,6 +2404,9 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D86" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="E86" s="7" t="n">
         <v>0</v>
       </c>
@@ -2391,6 +2424,9 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D87" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="E87" s="7" t="n">
         <v>0</v>
       </c>
@@ -2408,6 +2444,9 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D88" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="E88" s="7" t="n">
         <v>0</v>
       </c>
@@ -2425,6 +2464,9 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D89" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="E89" s="7" t="n">
         <v>0</v>
       </c>
@@ -2442,6 +2484,9 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D90" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="E90" s="7" t="n">
         <v>0</v>
       </c>
@@ -2459,6 +2504,9 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D91" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="E91" s="7" t="n">
         <v>0</v>
       </c>
@@ -2476,6 +2524,9 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D92" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="E92" s="7" t="n">
         <v>0</v>
       </c>
@@ -2493,6 +2544,9 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D93" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="E93" s="7" t="n">
         <v>0</v>
       </c>
@@ -2510,6 +2564,9 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D94" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="E94" s="7" t="n">
         <v>0</v>
       </c>
@@ -2527,6 +2584,9 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D95" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="E95" s="7" t="n">
         <v>0</v>
       </c>
@@ -2544,6 +2604,9 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D96" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="E96" s="7" t="n">
         <v>0</v>
       </c>
@@ -2561,6 +2624,9 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D97" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="E97" s="7" t="n">
         <v>0</v>
       </c>
@@ -2578,6 +2644,9 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D98" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E98" s="1" t="n">
         <v>1</v>
       </c>
@@ -2595,6 +2664,9 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D99" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E99" s="1" t="n">
         <v>1</v>
       </c>
@@ -2612,6 +2684,9 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D100" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E100" s="1" t="n">
         <v>1</v>
       </c>
@@ -2629,6 +2704,9 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D101" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E101" s="1" t="n">
         <v>1</v>
       </c>
@@ -2646,6 +2724,9 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D102" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="E102" s="1" t="n">
         <v>1</v>
       </c>
@@ -2663,6 +2744,9 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D103" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="E103" s="1" t="n">
         <v>1</v>
       </c>
@@ -2680,6 +2764,9 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D104" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="E104" s="1" t="n">
         <v>1</v>
       </c>
@@ -2697,6 +2784,9 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D105" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="E105" s="1" t="n">
         <v>1</v>
       </c>
@@ -2714,6 +2804,9 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D106" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E106" s="1" t="n">
         <v>1</v>
       </c>
@@ -2731,6 +2824,9 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D107" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E107" s="1" t="n">
         <v>1</v>
       </c>
@@ -2748,6 +2844,9 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D108" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E108" s="1" t="n">
         <v>1</v>
       </c>
@@ -2765,6 +2864,9 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D109" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E109" s="1" t="n">
         <v>1</v>
       </c>
@@ -2782,6 +2884,9 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D110" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="E110" s="1" t="n">
         <v>1</v>
       </c>
@@ -2799,6 +2904,9 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D111" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="E111" s="1" t="n">
         <v>1</v>
       </c>
@@ -2816,6 +2924,9 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D112" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="E112" s="1" t="n">
         <v>1</v>
       </c>
@@ -2833,6 +2944,9 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D113" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="E113" s="1" t="n">
         <v>1</v>
       </c>

--- a/TermProject/exponentiationfsm_state_table.xlsx
+++ b/TermProject/exponentiationfsm_state_table.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t xml:space="preserve">Inputs</t>
   </si>
@@ -122,21 +122,9 @@
     <t xml:space="preserve">ready_out </t>
   </si>
   <si>
-    <t xml:space="preserve">mux_control_in[7..0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a[255..0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">load_result</t>
-  </si>
-  <si>
     <t xml:space="preserve">Counter</t>
   </si>
   <si>
-    <t xml:space="preserve">mux_control_out[8..0]</t>
-  </si>
-  <si>
     <t xml:space="preserve">valid_out </t>
   </si>
   <si>
@@ -146,67 +134,118 @@
     <t xml:space="preserve">next state</t>
   </si>
   <si>
-    <t xml:space="preserve">reset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">counting</t>
+    <t xml:space="preserve">xx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COUNTING</t>
   </si>
   <si>
     <t xml:space="preserve">Counter = counter + 1</t>
   </si>
   <si>
-    <t xml:space="preserve">finished</t>
-  </si>
-  <si>
     <t xml:space="preserve">Counter =  counter + 1</t>
   </si>
   <si>
     <t xml:space="preserve">mux_ctrl_R_in[3..0]</t>
   </si>
   <si>
-    <t xml:space="preserve">R_OUT</t>
+    <t xml:space="preserve">R_sel</t>
   </si>
   <si>
     <t xml:space="preserve">A[255]</t>
   </si>
   <si>
+    <t xml:space="preserve">R_sel[3..0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boolean Function</t>
+  </si>
+  <si>
     <t xml:space="preserve">S5[256]</t>
   </si>
   <si>
     <t xml:space="preserve">S4[256]</t>
   </si>
   <si>
+    <t xml:space="preserve">b101</t>
+  </si>
+  <si>
     <t xml:space="preserve">S5</t>
   </si>
   <si>
+    <t xml:space="preserve">nor(A, MR[3])</t>
+  </si>
+  <si>
     <t xml:space="preserve">S3[256]</t>
   </si>
   <si>
+    <t xml:space="preserve">S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and(A, MR[2])</t>
+  </si>
+  <si>
     <t xml:space="preserve">S2[256]</t>
   </si>
   <si>
-    <t xml:space="preserve">S5 = !A[255] &amp;&amp; !mux_ctrl_R_in[3]</t>
-  </si>
-  <si>
     <t xml:space="preserve">S3</t>
   </si>
   <si>
+    <t xml:space="preserve">b011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nor(A, MR[3], MR[1])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and(A, MR[2], MR[0])</t>
+  </si>
+  <si>
     <t xml:space="preserve">S1</t>
   </si>
   <si>
-    <t xml:space="preserve">S4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2</t>
+    <t xml:space="preserve">b001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and(A, MR[3], MR[1])</t>
   </si>
   <si>
     <t xml:space="preserve">S0</t>
   </si>
   <si>
+    <t xml:space="preserve">b000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forkortelser:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mux_ctrl_R_in[]</t>
+  </si>
+  <si>
     <t xml:space="preserve">mux_ctrl_P_in[3..0]</t>
   </si>
   <si>
-    <t xml:space="preserve">P_OUT</t>
+    <t xml:space="preserve">P_sel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_sel[3..0]</t>
   </si>
   <si>
     <t xml:space="preserve">S11[256]</t>
@@ -218,25 +257,46 @@
     <t xml:space="preserve">S11</t>
   </si>
   <si>
+    <t xml:space="preserve">nor(A, MP[3])</t>
+  </si>
+  <si>
     <t xml:space="preserve">S9[256]</t>
   </si>
   <si>
+    <t xml:space="preserve">s10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and(A, MP[2])</t>
+  </si>
+  <si>
     <t xml:space="preserve">S8[256]</t>
   </si>
   <si>
     <t xml:space="preserve">S9</t>
   </si>
   <si>
+    <t xml:space="preserve">nor(A, MP[3], MP[1])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and(A, MP[2], MP[0])</t>
+  </si>
+  <si>
     <t xml:space="preserve">S7</t>
   </si>
   <si>
+    <t xml:space="preserve">and(A, MP[3], MP[1])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP[]</t>
+  </si>
+  <si>
     <t xml:space="preserve">S10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S6</t>
   </si>
 </sst>
 </file>
@@ -320,7 +380,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -341,15 +401,19 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -557,6 +621,7 @@
   <dimension ref="A1:XFD30"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="2" width="19.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12.29"/>
@@ -1149,326 +1214,315 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:N113"/>
+  <dimension ref="A1:N1048576"/>
   <sheetFormatPr defaultColWidth="10.60546875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.61"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="15.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="1" width="12.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="20.38"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="1" width="10.61"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M1" s="0"/>
+    </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="0"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="K2" s="6"/>
-      <c r="L2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="M2" s="0"/>
+      <c r="N2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="G3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="M3" s="0"/>
+      <c r="N3" s="0"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0"/>
+      <c r="B4" s="0"/>
+      <c r="C4" s="0"/>
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="L4" s="7"/>
+      <c r="M4" s="0"/>
+      <c r="N4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0"/>
+      <c r="B5" s="0"/>
+      <c r="C5" s="0"/>
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="7"/>
+      <c r="M5" s="0"/>
+      <c r="N5" s="0"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0"/>
+      <c r="B6" s="0"/>
+      <c r="C6" s="0"/>
+      <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="L6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="0"/>
+      <c r="N6" s="0"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0"/>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
+      <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0"/>
-      <c r="F4" s="0"/>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1" t="s">
+      <c r="M7" s="0"/>
+      <c r="N7" s="0"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
+      <c r="C8" s="0"/>
+      <c r="D8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="0"/>
-      <c r="F5" s="0"/>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
-      <c r="G6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="0"/>
-      <c r="F7" s="0"/>
-      <c r="G7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="0"/>
-      <c r="F8" s="0"/>
-      <c r="G8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="M8" s="0"/>
+      <c r="N8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="0"/>
-      <c r="F9" s="0"/>
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="0"/>
-      <c r="F10" s="0"/>
-      <c r="L10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A10" s="0"/>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+      <c r="D10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="0"/>
+      <c r="N10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0"/>
+      <c r="B23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0"/>
@@ -1483,60 +1537,106 @@
       <c r="B26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0"/>
+      <c r="A27" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="B27" s="0"/>
+      <c r="C27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="L27" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="0"/>
-      <c r="D28" s="1" t="s">
+      <c r="A28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="0"/>
-      <c r="F29" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D29" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="1" t="n">
@@ -1549,20 +1649,33 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="1" t="n">
@@ -1572,23 +1685,29 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="1" t="n">
@@ -1601,37 +1720,59 @@
         <v>1</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D33" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D34" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="7" t="n">
+      <c r="A34" s="0"/>
+      <c r="C34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="1" t="n">
@@ -1644,15 +1785,26 @@
         <v>0</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0"/>
-      <c r="D35" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="7" t="n">
+      <c r="C35" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="1" t="n">
@@ -1662,17 +1814,20 @@
         <v>1</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D36" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="7" t="n">
+      <c r="C36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="1" t="n">
@@ -1685,36 +1840,51 @@
         <v>1</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D37" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="7" t="n">
+      <c r="B37" s="9"/>
+      <c r="C37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K37" s="8"/>
+      <c r="L37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="7" t="n">
+      <c r="C38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="1" t="n">
@@ -1727,15 +1897,24 @@
         <v>0</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="L38" s="0"/>
+      <c r="M38" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D39" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="7" t="n">
+      <c r="C39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="1" t="n">
@@ -1745,17 +1924,23 @@
         <v>0</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L39" s="0"/>
+      <c r="M39" s="0"/>
+      <c r="N39" s="0"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="7" t="n">
+      <c r="C40" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="1" t="n">
@@ -1768,36 +1953,43 @@
         <v>1</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D41" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="7" t="n">
+      <c r="A41" s="0"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0"/>
-      <c r="B42" s="10"/>
-      <c r="D42" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="7" t="n">
+      <c r="C42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="1" t="n">
@@ -1810,15 +2002,18 @@
         <v>0</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0"/>
-      <c r="D43" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="7" t="n">
+      <c r="A43" s="8"/>
+      <c r="C43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="1" t="n">
@@ -1828,18 +2023,20 @@
         <v>1</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7"/>
-      <c r="D44" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E44" s="7" t="n">
+      <c r="C44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="1" t="n">
@@ -1852,32 +2049,38 @@
         <v>1</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D45" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>0</v>
+      <c r="C45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D46" s="8" t="s">
-        <v>57</v>
+      <c r="C46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>1</v>
@@ -1892,12 +2095,15 @@
         <v>0</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D47" s="8" t="s">
-        <v>57</v>
+      <c r="C47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>1</v>
@@ -1909,15 +2115,18 @@
         <v>0</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D48" s="8" t="s">
-        <v>57</v>
+      <c r="C48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>1</v>
@@ -1932,12 +2141,15 @@
         <v>1</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D49" s="8" t="s">
-        <v>57</v>
+      <c r="C49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>1</v>
@@ -1946,18 +2158,21 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D50" s="8" t="s">
-        <v>58</v>
+      <c r="C50" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>1</v>
@@ -1972,12 +2187,15 @@
         <v>0</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D51" s="8" t="s">
-        <v>59</v>
+      <c r="C51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>1</v>
@@ -1989,15 +2207,18 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D52" s="8" t="s">
-        <v>58</v>
+      <c r="C52" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>1</v>
@@ -2012,32 +2233,38 @@
         <v>1</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D53" s="8" t="s">
-        <v>59</v>
+      <c r="C53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D54" s="8" t="s">
-        <v>57</v>
+      <c r="C54" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>1</v>
@@ -2052,12 +2279,15 @@
         <v>0</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D55" s="8" t="s">
-        <v>57</v>
+      <c r="C55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>1</v>
@@ -2069,15 +2299,18 @@
         <v>0</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D56" s="8" t="s">
-        <v>57</v>
+      <c r="C56" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>1</v>
@@ -2092,12 +2325,15 @@
         <v>1</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D57" s="8" t="s">
-        <v>57</v>
+      <c r="C57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>1</v>
@@ -2106,18 +2342,21 @@
         <v>1</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D58" s="8" t="s">
-        <v>58</v>
+      <c r="C58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>1</v>
@@ -2132,12 +2371,15 @@
         <v>0</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D59" s="8" t="s">
-        <v>59</v>
+      <c r="C59" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>1</v>
@@ -2149,15 +2391,18 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D60" s="8" t="s">
-        <v>58</v>
+      <c r="C60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>1</v>
@@ -2172,32 +2417,20 @@
         <v>1</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D61" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="D61" s="0"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="0"/>
+      <c r="G61" s="0"/>
+      <c r="H61" s="0"/>
+      <c r="I61" s="0"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D62" s="0"/>
-      <c r="E62" s="0"/>
+      <c r="E62" s="8"/>
       <c r="F62" s="0"/>
       <c r="G62" s="0"/>
       <c r="H62" s="0"/>
@@ -2205,7 +2438,7 @@
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D63" s="0"/>
-      <c r="E63" s="0"/>
+      <c r="E63" s="8"/>
       <c r="F63" s="0"/>
       <c r="G63" s="0"/>
       <c r="H63" s="0"/>
@@ -2213,7 +2446,7 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D64" s="0"/>
-      <c r="E64" s="0"/>
+      <c r="E64" s="8"/>
       <c r="F64" s="0"/>
       <c r="G64" s="0"/>
       <c r="H64" s="0"/>
@@ -2221,7 +2454,7 @@
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D65" s="0"/>
-      <c r="E65" s="0"/>
+      <c r="E65" s="8"/>
       <c r="F65" s="0"/>
       <c r="G65" s="0"/>
       <c r="H65" s="0"/>
@@ -2229,7 +2462,7 @@
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D66" s="0"/>
-      <c r="E66" s="0"/>
+      <c r="E66" s="8"/>
       <c r="F66" s="0"/>
       <c r="G66" s="0"/>
       <c r="H66" s="0"/>
@@ -2237,7 +2470,7 @@
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D67" s="0"/>
-      <c r="E67" s="0"/>
+      <c r="E67" s="8"/>
       <c r="F67" s="0"/>
       <c r="G67" s="0"/>
       <c r="H67" s="0"/>
@@ -2245,7 +2478,7 @@
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D68" s="0"/>
-      <c r="E68" s="0"/>
+      <c r="E68" s="8"/>
       <c r="F68" s="0"/>
       <c r="G68" s="0"/>
       <c r="H68" s="0"/>
@@ -2253,679 +2486,865 @@
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D69" s="0"/>
-      <c r="E69" s="0"/>
+      <c r="E69" s="8"/>
       <c r="F69" s="0"/>
       <c r="G69" s="0"/>
       <c r="H69" s="0"/>
       <c r="I69" s="0"/>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D70" s="0"/>
-      <c r="E70" s="0"/>
-      <c r="F70" s="0"/>
-      <c r="G70" s="0"/>
-      <c r="H70" s="0"/>
-      <c r="I70" s="0"/>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D79" s="9"/>
+      <c r="E79" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="L79" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="M79" s="9"/>
+      <c r="N79" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
+      <c r="A80" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E80" s="8"/>
+      <c r="F80" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E81" s="0"/>
-      <c r="F81" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G81" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H81" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>76</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N81" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D82" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N82" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N83" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C84" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N84" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C85" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E82" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D83" s="8" t="s">
+      <c r="N85" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C86" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N86" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C87" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C88" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C89" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M89" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N89" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C90" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="0"/>
+      <c r="M90" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="N90" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C91" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E83" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D84" s="8" t="s">
+      <c r="D91" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C92" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E84" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D85" s="8" t="s">
+      <c r="D92" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C93" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C94" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C95" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D86" s="8" t="s">
+      <c r="D95" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C96" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E86" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D87" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E87" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D88" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E88" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D89" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E89" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D90" s="8" t="s">
+      <c r="D96" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C97" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C99" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C100" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C101" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C102" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E90" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D91" s="8" t="s">
+      <c r="D102" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C103" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C104" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D92" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E92" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D93" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E93" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I93" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D94" s="8" t="s">
+      <c r="D104" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C105" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C106" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C107" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C108" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C109" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E94" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D95" s="8" t="s">
+      <c r="D110" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C112" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D96" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D97" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I97" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D98" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E98" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D99" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E99" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D100" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E100" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I100" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D101" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I101" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D102" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D103" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E103" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D104" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E104" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I104" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D105" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E105" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I105" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D106" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E106" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D107" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E107" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D108" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E108" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I108" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D109" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E109" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I109" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D110" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E110" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D111" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E111" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D112" s="8" t="s">
-        <v>70</v>
+      <c r="D112" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="E112" s="1" t="n">
         <v>1</v>
@@ -2940,37 +3359,21 @@
         <v>1</v>
       </c>
       <c r="I112" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D113" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I113" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="F80:I80"/>
+  <mergeCells count="9">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="L79:M79"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
